--- a/VerveStacks_BRA_grids_kan10/SuppXLS/trades/scentrade__trade_links.xlsx
+++ b/VerveStacks_BRA_grids_kan10/SuppXLS/trades/scentrade__trade_links.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_BRA_grids_kan10\SuppXLS\trades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{51AE8BAF-176F-4635-A1EA-58F3EFC702D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{0B55A4EC-8614-4F20-B8D0-858B4D6B46D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{859F879F-DEC5-4237-908F-4DF342E9A811}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{6E2CD2E3-7010-42BE-90C1-996D0FA1FBFF}"/>
   </bookViews>
   <sheets>
     <sheet name="grid_links" sheetId="1" r:id="rId1"/>
@@ -742,7 +742,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{605FF822-BC0E-4429-92DB-1C9F0B2528D6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2826C5BE-83A7-43AF-B9B0-1DF512F3ADDE}">
   <dimension ref="B3:L41"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_BRA_grids_kan10/SuppXLS/trades/scentrade__trade_links.xlsx
+++ b/VerveStacks_BRA_grids_kan10/SuppXLS/trades/scentrade__trade_links.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_BRA_grids_kan10\SuppXLS\trades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0B55A4EC-8614-4F20-B8D0-858B4D6B46D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{C5A8A24E-33E5-4FB7-8BAE-C831090EEBD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{6E2CD2E3-7010-42BE-90C1-996D0FA1FBFF}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{3C4C3061-ECD4-4B76-8B83-75DD90DACE3A}"/>
   </bookViews>
   <sheets>
     <sheet name="grid_links" sheetId="1" r:id="rId1"/>
@@ -742,7 +742,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2826C5BE-83A7-43AF-B9B0-1DF512F3ADDE}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3ADC88DD-2C81-446F-B40F-0EB3D99C6744}">
   <dimension ref="B3:L41"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
